--- a/Result/profitability/8215.xlsx
+++ b/Result/profitability/8215.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,13 +668,13 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>15.2725</v>
+        <v>14.35375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>13.815</v>
+        <v>13.5825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>10.775</v>
+        <v>10.1225</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>8.33</v>
+        <v>8.907500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>8.6625</v>
+        <v>8.52875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>8.609999999999999</v>
+        <v>9.11875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>8.428750000000001</v>
+        <v>8.813750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9534,6 +9534,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>8215</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4946</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4205</v>
+      </c>
+      <c r="E73" t="n">
+        <v>740</v>
+      </c>
+      <c r="F73" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-2.12%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>39</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-102</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-0.2275</v>
+      </c>
+      <c r="N73" t="n">
+        <v>15.43625</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.2590412111017661</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>4.620000000000001</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.4463768115942031</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
